--- a/resources/templates/standard/A6100-02.xlsx
+++ b/resources/templates/standard/A6100-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>제 안 관 리 대 장</t>
   </si>
@@ -630,12 +633,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -781,20 +786,20 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -802,7 +807,7 @@
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
@@ -816,17 +821,17 @@
       <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5" s="5"/>
       <c r="AB5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
       <c r="AE5" s="5"/>
       <c r="AF5" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG5" s="8"/>
       <c r="AH5" s="8"/>
@@ -841,13 +846,13 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
       <c r="K6" s="12"/>
       <c r="L6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6" s="12"/>
       <c r="N6" s="5"/>
@@ -869,11 +874,11 @@
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
       <c r="AF6" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG6" s="11"/>
       <c r="AH6" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI6" s="13"/>
     </row>
